--- a/app/form.xlsx
+++ b/app/form.xlsx
@@ -53,16 +53,16 @@
     <t>이관</t>
   </si>
   <si>
-    <t>010-0000-0000</t>
+    <t>010-1234-5678</t>
   </si>
   <si>
     <t>밸류업</t>
   </si>
   <si>
-    <t>김예시</t>
-  </si>
-  <si>
-    <t>010-0000-0001</t>
+    <t>김주호</t>
+  </si>
+  <si>
+    <t>010-8765-4321</t>
   </si>
   <si>
     <t>분류</t>
@@ -77,16 +77,16 @@
     <t>지역</t>
   </si>
   <si>
-    <t>1985</t>
+    <t>1988</t>
   </si>
   <si>
     <t>역삼동</t>
   </si>
   <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>수원시 영통구</t>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>수원시 장안구</t>
   </si>
   <si>
     <t>월</t>

--- a/app/form.xlsx
+++ b/app/form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\한호자산연구소\1_부서\개발팀\주피터_앱\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0333D578-E84D-40BE-8AC6-34BF09B9EA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96253893-FA56-482D-8CAC-540901F143BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D32EFEA-BC06-41A7-A68F-4210D974FE5C}"/>
+    <workbookView xWindow="2265" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{CB8133E8-AD2A-4EBB-A365-9C0AC0158294}"/>
   </bookViews>
   <sheets>
     <sheet name="명단" sheetId="1" r:id="rId1"/>
@@ -39,78 +39,116 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>성격</t>
   </si>
   <si>
+    <t>월</t>
+  </si>
+  <si>
     <t>이름</t>
   </si>
   <si>
+    <t>생년</t>
+  </si>
+  <si>
+    <t>지역</t>
+  </si>
+  <si>
     <t>연락처</t>
   </si>
   <si>
     <t>이관</t>
   </si>
   <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>김주성</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>역삼동</t>
+  </si>
+  <si>
     <t>010-1234-5678</t>
   </si>
   <si>
-    <t>밸류업</t>
+    <t>그룹2</t>
   </si>
   <si>
     <t>김주호</t>
   </si>
   <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>수원시 장안구</t>
+  </si>
+  <si>
     <t>010-8765-4321</t>
   </si>
   <si>
-    <t>분류</t>
-  </si>
-  <si>
-    <t>2026-10</t>
-  </si>
-  <si>
-    <t>생년</t>
-  </si>
-  <si>
-    <t>지역</t>
-  </si>
-  <si>
-    <t>1988</t>
-  </si>
-  <si>
-    <t>역삼동</t>
-  </si>
-  <si>
-    <t>1989</t>
-  </si>
-  <si>
-    <t>수원시 장안구</t>
-  </si>
-  <si>
-    <t>월</t>
+    <t>그룹</t>
+  </si>
+  <si>
+    <t>그룹1</t>
+  </si>
+  <si>
+    <t>한신지점</t>
+  </si>
+  <si>
+    <t>쇼핑엔티</t>
+  </si>
+  <si>
+    <t>그룹3</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>쇼핑엔티</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김주성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>그룹4</t>
+  </si>
+  <si>
+    <t>그룹5</t>
+  </si>
+  <si>
+    <t>그룹6</t>
+  </si>
+  <si>
+    <t>그룹7</t>
+  </si>
+  <si>
+    <t>그룹8</t>
+  </si>
+  <si>
+    <t>그룹9</t>
+  </si>
+  <si>
+    <t>그룹10</t>
+  </si>
+  <si>
+    <t>← 성격 칸: 이관 또는 그룹1~그룹10. 그룹 이름은 왼쪽 표에 적으세요 (안 쓰는 그룹은 비워 두기)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -126,14 +164,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,17 +181,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9DCEA"/>
+        <fgColor rgb="FFDDE6F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEBCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -161,14 +227,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -504,91 +582,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69439D7-5F82-4E01-83B3-8CFEA7EE3659}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCB9D0B-991C-4CCB-843E-0834FE6FB454}">
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.625" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/app/form.xlsx
+++ b/app/form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\한호자산연구소\1_부서\개발팀\주피터_앱\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96253893-FA56-482D-8CAC-540901F143BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0333D578-E84D-40BE-8AC6-34BF09B9EA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{CB8133E8-AD2A-4EBB-A365-9C0AC0158294}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D32EFEA-BC06-41A7-A68F-4210D974FE5C}"/>
   </bookViews>
   <sheets>
     <sheet name="명단" sheetId="1" r:id="rId1"/>
@@ -39,116 +39,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>성격</t>
   </si>
   <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>연락처</t>
+  </si>
+  <si>
+    <t>이관</t>
+  </si>
+  <si>
+    <t>010-1234-5678</t>
+  </si>
+  <si>
+    <t>밸류업</t>
+  </si>
+  <si>
+    <t>김주호</t>
+  </si>
+  <si>
+    <t>010-8765-4321</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>생년</t>
+  </si>
+  <si>
+    <t>지역</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>역삼동</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>수원시 장안구</t>
+  </si>
+  <si>
     <t>월</t>
   </si>
   <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>생년</t>
-  </si>
-  <si>
-    <t>지역</t>
-  </si>
-  <si>
-    <t>연락처</t>
-  </si>
-  <si>
-    <t>이관</t>
-  </si>
-  <si>
-    <t>2026-10</t>
+    <t/>
+  </si>
+  <si>
+    <t>쇼핑엔티</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김주성</t>
-  </si>
-  <si>
-    <t>1988</t>
-  </si>
-  <si>
-    <t>역삼동</t>
-  </si>
-  <si>
-    <t>010-1234-5678</t>
-  </si>
-  <si>
-    <t>그룹2</t>
-  </si>
-  <si>
-    <t>김주호</t>
-  </si>
-  <si>
-    <t>1989</t>
-  </si>
-  <si>
-    <t>수원시 장안구</t>
-  </si>
-  <si>
-    <t>010-8765-4321</t>
-  </si>
-  <si>
-    <t>그룹</t>
-  </si>
-  <si>
-    <t>그룹1</t>
-  </si>
-  <si>
-    <t>한신지점</t>
-  </si>
-  <si>
-    <t>쇼핑엔티</t>
-  </si>
-  <si>
-    <t>그룹3</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>그룹4</t>
-  </si>
-  <si>
-    <t>그룹5</t>
-  </si>
-  <si>
-    <t>그룹6</t>
-  </si>
-  <si>
-    <t>그룹7</t>
-  </si>
-  <si>
-    <t>그룹8</t>
-  </si>
-  <si>
-    <t>그룹9</t>
-  </si>
-  <si>
-    <t>그룹10</t>
-  </si>
-  <si>
-    <t>← 성격 칸: 이관 또는 그룹1~그룹10. 그룹 이름은 왼쪽 표에 적으세요 (안 쓰는 그룹은 비워 두기)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -164,15 +126,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,44 +142,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE6F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEBCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFD9DCEA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -227,26 +161,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,238 +504,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCB9D0B-991C-4CCB-843E-0834FE6FB454}">
-  <dimension ref="A1:K12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69439D7-5F82-4E01-83B3-8CFEA7EE3659}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.625" customWidth="1"/>
-    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>